--- a/liaisons_Super_Constellation/Reseau_Lufthansa_L1049G_sourced.xlsx
+++ b/liaisons_Super_Constellation/Reseau_Lufthansa_L1049G_sourced.xlsx
@@ -756,6 +756,33 @@
       <c r="A12" t="str">
         <v>[R] Vols retour ajoutés automatiquement (itinéraire miroir, horaires reconstitués).</v>
       </c>
+      <c r="B12" t="str">
+        <v/>
+      </c>
+      <c r="C12" t="str">
+        <v/>
+      </c>
+      <c r="D12" t="str">
+        <v/>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v/>
+      </c>
+      <c r="J12" t="str">
+        <v/>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -852,7 +879,7 @@
         <v>16:00</v>
       </c>
       <c r="E3" t="str">
-        <v>Rio de Janeiro (GIG) (22:00 / 22:00)</v>
+        <v>Rio de Janeiro (GIG) (22:00 / 22:45)</v>
       </c>
       <c r="F3" t="str">
         <v>Dakar (DKR) (05:45 * / 07:15 *)</v>
@@ -1121,6 +1148,36 @@
     <row r="11">
       <c r="A11" t="str">
         <v>[R] Vols retour ajoutés automatiquement (itinéraire miroir, horaires reconstitués).</v>
+      </c>
+      <c r="B11" t="str">
+        <v/>
+      </c>
+      <c r="C11" t="str">
+        <v/>
+      </c>
+      <c r="D11" t="str">
+        <v/>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v/>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
